--- a/health_coach_forms/007_health_coaching_certification_workshop_registration--health_coach_forms.xlsx
+++ b/health_coach_forms/007_health_coaching_certification_workshop_registration--health_coach_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>agreements</t>
+          <t>training_provider</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Agreements</t>
+          <t>Training Provider</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>participant_signature</t>
+          <t>training_academy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Participant Signature</t>
+          <t>Training Academy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>training_provider</t>
+          <t>workshop_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Training Provider</t>
+          <t>Workshop Information</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>training_academy</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Training Academy</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>workshop_date</t>
+          <t>agreements</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Workshop Date</t>
+          <t>Agreements</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,251 +676,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>workshop_time</t>
+          <t>participant_signature</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Workshop Time</t>
+          <t>Participant Signature</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>contact_email</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Contact E-mail</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>contact_phone</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Contact Phone</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>agreements_text</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Agreements</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>participant_signature_2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Participant Signature</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>training_provider_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Training Provider</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>training_academy_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Training Academy</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>workshop_date_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Workshop Date</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>workshop_time_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Workshop Time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>contact_email_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Contact E-mail</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>contact_phone_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Contact Phone</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -937,10 +707,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1178,108 +948,6 @@
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t>Academy 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>training_provider_2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>provider_1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Provider 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>training_provider_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>provider_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Provider 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>training_provider_2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>provider_3</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Provider 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>training_academy_2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>academy_1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Academy 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>training_academy_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>academy_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Academy 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>training_academy_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>academy_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>Academy 3</t>
         </is>
